--- a/QSExt/Resource/GoGoalDBInfo.xlsx
+++ b/QSExt/Resource/GoGoalDBInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hst/Project/QSExt/QSExt/Resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBC7CD1-D679-CE49-AA2E-1478884519F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869FD7F0-E7B2-5A4E-BA1F-7C1A51E2BA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6680" yWindow="3080" windowWidth="26800" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6680" yWindow="3080" windowWidth="26800" windowHeight="16560" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TableInfo" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26004" uniqueCount="3544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26004" uniqueCount="3548">
   <si>
     <t>TableName</t>
   </si>
@@ -11128,6 +11128,22 @@
   </si>
   <si>
     <t>52周一致预期净利润变化率</t>
+  </si>
+  <si>
+    <t>YearMonthMappingTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Month</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EndYear</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EndMonth</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11498,7 +11514,7 @@
   <cols>
     <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.6640625" customWidth="1"/>
@@ -11617,7 +11633,7 @@
         <v>272</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
+        <v>3544</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>463</v>
@@ -15969,7 +15985,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -15986,7 +16002,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>209</v>
+        <v>17</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -16054,7 +16070,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>209</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -16071,7 +16087,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>209</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -16088,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>209</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -16105,7 +16121,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>209</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="153" spans="1:5">
